--- a/src/wattio/data/core_geometry_db.xlsx
+++ b/src/wattio/data/core_geometry_db.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,34 +611,59 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>E 42/33/20</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>42.15</v>
+      </c>
+      <c r="C6" t="n">
+        <v>32.59999999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>236</v>
+      </c>
+      <c r="I6" t="n">
+        <v>145</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34200</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>E 55/28/21</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
         <v>55.15000000000001</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C7" t="n">
         <v>27.5</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>20.6</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E7" t="n">
         <v>18.9</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F7" t="n">
         <v>38.25</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G7" t="n">
         <v>16.95</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H7" t="n">
         <v>354</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I7" t="n">
         <v>124</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7" t="n">
         <v>43900</v>
       </c>
     </row>
@@ -653,7 +678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -842,6 +867,81 @@
       </c>
       <c r="J5" t="n">
         <v>17800</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ETD 49/25/16</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="C6" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>211</v>
+      </c>
+      <c r="I6" t="n">
+        <v>114</v>
+      </c>
+      <c r="J6" t="n">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ETD 54/28/19</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>53.85</v>
+      </c>
+      <c r="C7" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="D7" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="H7" t="n">
+        <v>280</v>
+      </c>
+      <c r="I7" t="n">
+        <v>127</v>
+      </c>
+      <c r="J7" t="n">
+        <v>35500</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ETD 59/31/22</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>59.15</v>
+      </c>
+      <c r="C8" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="D8" t="n">
+        <v>21.425</v>
+      </c>
+      <c r="H8" t="n">
+        <v>368</v>
+      </c>
+      <c r="I8" t="n">
+        <v>139</v>
+      </c>
+      <c r="J8" t="n">
+        <v>51500</v>
       </c>
     </row>
   </sheetData>
@@ -855,7 +955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1138,6 +1238,31 @@
       </c>
       <c r="M6" t="n">
         <v>17600</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PQ 50/50</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C7" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>32</v>
+      </c>
+      <c r="K7" t="n">
+        <v>328</v>
+      </c>
+      <c r="L7" t="n">
+        <v>113</v>
+      </c>
+      <c r="M7" t="n">
+        <v>37100</v>
       </c>
     </row>
   </sheetData>
